--- a/templates/wfh_data_template.xlsx
+++ b/templates/wfh_data_template.xlsx
@@ -14,11 +14,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
   <si>
     <t>RD Name</t>
   </si>
   <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>RD Category</t>
+  </si>
+  <si>
     <t>Start Date</t>
   </si>
   <si>
@@ -28,19 +34,40 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>John Doe</t>
-  </si>
-  <si>
-    <t>Jane Smith</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>2025-09-08</t>
-  </si>
-  <si>
-    <t>2025-09-10</t>
+    <t>abc</t>
+  </si>
+  <si>
+    <t>MTB_WCS_MSE7_MS25</t>
+  </si>
+  <si>
+    <t>Vendor</t>
+  </si>
+  <si>
+    <t>7/16/2025</t>
+  </si>
+  <si>
+    <t>7/7/2025</t>
+  </si>
+  <si>
+    <t>6/20/2025</t>
+  </si>
+  <si>
+    <t>6/4/2025</t>
+  </si>
+  <si>
+    <t>5/30/2025</t>
+  </si>
+  <si>
+    <t>5/26/2025</t>
+  </si>
+  <si>
+    <t>5/20/2025</t>
+  </si>
+  <si>
+    <t>8/5/2025</t>
+  </si>
+  <si>
+    <t>5/27/2025</t>
   </si>
 </sst>
 </file>
@@ -398,10 +425,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -414,24 +441,36 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
@@ -439,8 +478,134 @@
       <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="D3">
-        <v>3</v>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
